--- a/results/final_0624_summary/Yeast_PartialAbstention_summary.xlsx
+++ b/results/final_0624_summary/Yeast_PartialAbstention_summary.xlsx
@@ -586,57 +586,141 @@
           <t>0.0210±0.0033</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0557±0.0042</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.1655±0.0154</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.3690±0.0153</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0.2155±0.0181</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.4444±0.0193</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.7755±0.0290</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.9474±0.0175</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>0.8197±0.0053</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.8275±0.0059</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.8458±0.0048</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.8640±0.0063</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>0.6671±0.0063</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.6699±0.0080</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.6745±0.0048</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.6612±0.0055</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>0.8158±0.0052</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.8174±0.0059</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.8152±0.0047</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.7845±0.0086</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0.2445±0.0202</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.2398±0.0211</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.2327±0.0204</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.2147±0.0293</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>0.2445±0.0202</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.2398±0.0211</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.2327±0.0204</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.2112±0.0293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -649,57 +733,141 @@
           <t>0.0217±0.0030</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0560±0.0041</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.1656±0.0154</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.3688±0.0154</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0.2230±0.0164</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.4481±0.0180</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.7768±0.0310</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.9483±0.0172</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>0.8190±0.0060</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.8253±0.0062</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.8438±0.0055</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.8618±0.0066</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>0.6749±0.0066</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6721±0.0081</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6752±0.0050</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6601±0.0054</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>0.8149±0.0060</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.8149±0.0062</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.8128±0.0055</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7810±0.0092</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0.2404±0.0203</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.2278±0.0172</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.2195±0.0211</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.2040±0.0250</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0.2404±0.0203</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.2278±0.0172</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.2195±0.0211</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.2003±0.0249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -712,57 +880,141 @@
           <t>0.0210±0.0033</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0556±0.0041</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.1653±0.0154</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.3689±0.0153</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>0.2151±0.0182</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.4437±0.0192</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.7751±0.0292</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.9472±0.0178</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>0.8194±0.0052</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.8273±0.0059</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.8457±0.0049</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.8639±0.0064</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>0.6669±0.0062</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.6697±0.0082</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.6745±0.0052</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.6612±0.0054</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>0.8156±0.0052</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.8172±0.0058</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.8151±0.0048</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.7844±0.0087</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0.2449±0.0205</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.2400±0.0208</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.2327±0.0204</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.2149±0.0289</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0.2449±0.0205</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.2400±0.0208</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.2327±0.0204</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.2114±0.0290</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -775,57 +1027,141 @@
           <t>0.0216±0.0029</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0559±0.0041</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.1653±0.0153</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.3686±0.0153</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>0.2209±0.0171</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.4468±0.0178</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.7766±0.0311</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.9477±0.0178</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>0.8185±0.0059</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.8251±0.0062</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.8434±0.0054</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.8614±0.0067</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>0.6744±0.0061</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.6719±0.0081</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.6748±0.0051</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.6597±0.0055</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>0.8145±0.0058</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.8147±0.0062</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.8124±0.0056</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.7805±0.0093</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0.2404±0.0193</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.2271±0.0176</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.2189±0.0206</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.2040±0.0246</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0.2404±0.0193</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.2271±0.0176</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.2189±0.0206</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.2003±0.0246</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,57 +1174,141 @@
           <t>0.0001±0.0001</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0001±0.0001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0006±0.0004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0022±0.0008</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0.0008±0.0010</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0017±0.0015</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0081±0.0049</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0283±0.0105</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>0.8130±0.0040</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.8102±0.0041</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.8038±0.0047</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.7855±0.0056</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>0.6319±0.0076</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.6304±0.0075</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.6247±0.0080</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.6168±0.0058</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>0.8130±0.0040</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.8102±0.0041</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.8037±0.0047</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.7850±0.0057</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0.2003±0.0158</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.1893±0.0221</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.1651±0.0273</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.1235±0.0255</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>0.2003±0.0158</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.1893±0.0221</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.1651±0.0273</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.1235±0.0255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -901,57 +1321,141 @@
           <t>0.0005±0.0003</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0009±0.0003</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0024±0.0007</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0050±0.0014</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0.0070±0.0048</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.0116±0.0037</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0300±0.0082</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0633±0.0162</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>0.8045±0.0050</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.7970±0.0066</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.7753±0.0070</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.7085±0.0093</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>0.6664±0.0052</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.6636±0.0082</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.6512±0.0087</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.6052±0.0087</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>0.8044±0.0050</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.7968±0.0066</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.7747±0.0071</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.7070±0.0093</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0.2131±0.0197</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.1771±0.0226</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.1101±0.0146</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.0209±0.0096</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0.2131±0.0197</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.1771±0.0226</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.1101±0.0146</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0209±0.0096</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -964,57 +1468,141 @@
           <t>0.0001±0.0001</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0002±0.0002</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.0006±0.0004</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0022±0.0009</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0.0017±0.0015</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.0025±0.0022</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.0085±0.0049</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0296±0.0112</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>0.8102±0.0045</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.8080±0.0045</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.8028±0.0042</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.7840±0.0056</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>0.6164±0.0091</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.6161±0.0080</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.6141±0.0073</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0.6073±0.0065</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>0.8102±0.0044</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.8080±0.0045</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.8027±0.0043</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.7835±0.0056</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0.1796±0.0146</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.1647±0.0198</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.1487±0.0229</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.1157±0.0272</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0.1796±0.0146</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.1647±0.0198</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.1487±0.0229</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.1157±0.0272</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1027,57 +1615,141 @@
           <t>0.0005±0.0004</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0009±0.0003</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.0026±0.0008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0055±0.0015</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>0.0075±0.0053</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0118±0.0040</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0325±0.0087</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0691±0.0180</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>0.8050±0.0051</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7970±0.0069</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.7757±0.0070</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.7086±0.0094</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>0.6666±0.0055</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.6633±0.0084</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.6516±0.0084</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.6049±0.0088</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>0.8049±0.0051</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.7968±0.0069</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.7751±0.0071</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.7070±0.0093</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0.2139±0.0209</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.1761±0.0221</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.1103±0.0133</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.0199±0.0098</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0.2139±0.0209</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.1761±0.0221</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.1103±0.0133</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0199±0.0098</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
